--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.526157</v>
+        <v>0.305454</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.035857</v>
+        <v>0.021636</v>
       </c>
       <c r="C3" t="n">
-        <v>0.526157</v>
+        <v>0.305454</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009148</v>
+        <v>0.00441</v>
       </c>
       <c r="C4" t="n">
-        <v>0.562014</v>
+        <v>0.32709</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.571163</v>
+        <v>0.3315</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.305454</v>
+        <v>0.310539</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.021636</v>
+        <v>0.021525</v>
       </c>
       <c r="C3" t="n">
-        <v>0.305454</v>
+        <v>0.310539</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00441</v>
+        <v>0.004313</v>
       </c>
       <c r="C4" t="n">
-        <v>0.32709</v>
+        <v>0.332064</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3315</v>
+        <v>0.336378</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.310539</v>
+        <v>0.343367</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.021525</v>
+        <v>0.021585</v>
       </c>
       <c r="C3" t="n">
-        <v>0.310539</v>
+        <v>0.343367</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004313</v>
+        <v>0.00601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.332064</v>
+        <v>0.364952</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.336378</v>
+        <v>0.370963</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.343367</v>
+        <v>0.341237</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.021585</v>
+        <v>0.021318</v>
       </c>
       <c r="C3" t="n">
-        <v>0.343367</v>
+        <v>0.341237</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00601</v>
+        <v>0.006346</v>
       </c>
       <c r="C4" t="n">
-        <v>0.364952</v>
+        <v>0.362555</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.370963</v>
+        <v>0.3689</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.341237</v>
+        <v>0.280208</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.021318</v>
+        <v>0.016682</v>
       </c>
       <c r="C3" t="n">
-        <v>0.341237</v>
+        <v>0.280208</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006346</v>
+        <v>0.005319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.362555</v>
+        <v>0.29689</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3689</v>
+        <v>0.302208</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.280208</v>
+        <v>0.253831</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.016682</v>
+        <v>0.013325</v>
       </c>
       <c r="C3" t="n">
-        <v>0.280208</v>
+        <v>0.253831</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005319</v>
+        <v>0.007066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.29689</v>
+        <v>0.267156</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.302208</v>
+        <v>0.274223</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.253831</v>
+        <v>0.25523</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.013325</v>
+        <v>0.01364</v>
       </c>
       <c r="C3" t="n">
-        <v>0.253831</v>
+        <v>0.25523</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007066</v>
+        <v>0.006921</v>
       </c>
       <c r="C4" t="n">
-        <v>0.267156</v>
+        <v>0.26887</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.274223</v>
+        <v>0.275792</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.25523</v>
+        <v>0.260714</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01364</v>
+        <v>0.016742</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25523</v>
+        <v>0.260714</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006921</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.26887</v>
+        <v>0.277456</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.275792</v>
+        <v>0.277456</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.260714</v>
+        <v>0.258875</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.016742</v>
+        <v>0.016427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.260714</v>
+        <v>0.258875</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.277456</v>
+        <v>0.275302</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.277456</v>
+        <v>0.275302</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.258875</v>
+        <v>0.257426</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.016427</v>
+        <v>0.015614</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258875</v>
+        <v>0.257426</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.275302</v>
+        <v>0.27304</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.275302</v>
+        <v>0.273041</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.257426</v>
+        <v>0.258349</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015614</v>
+        <v>0.015106</v>
       </c>
       <c r="C3" t="n">
-        <v>0.257426</v>
+        <v>0.258349</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.27304</v>
+        <v>0.273455</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.273041</v>
+        <v>0.273454</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.258349</v>
+        <v>0.258728</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015106</v>
+        <v>0.014898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258349</v>
+        <v>0.258728</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.273455</v>
+        <v>0.273626</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.273454</v>
+        <v>0.273627</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.258728</v>
+        <v>0.293574</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.014898</v>
+        <v>0.015089</v>
       </c>
       <c r="C3" t="n">
-        <v>0.258728</v>
+        <v>0.293574</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.273626</v>
+        <v>0.308663</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.273627</v>
+        <v>0.308663</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.293574</v>
+        <v>0.293547</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015089</v>
+        <v>0.015153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.293574</v>
+        <v>0.293547</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.293547</v>
+        <v>0.297704</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015153</v>
+        <v>0.014891</v>
       </c>
       <c r="C3" t="n">
-        <v>0.293547</v>
+        <v>0.297704</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.014891</v>
+        <v>0.014898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.297704</v>
+        <v>0.297977</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>

--- a/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
+++ b/vignettes/vignette-2/old_to_new_waterfall_data.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.297977</v>
+        <v>0.304954</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.014898</v>
+        <v>0.015451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.297977</v>
+        <v>0.304954</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
     </row>
     <row r="5">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
